--- a/VERIFAI_KA152_Annex_Timetable.xlsx
+++ b/VERIFAI_KA152_Annex_Timetable.xlsx
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B2" s="45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>YEXMS01</t>
         </is>
       </c>
       <c r="C2" s="46" t="n"/>
@@ -2966,7 +2966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B2" s="45" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>PREPV02</t>
         </is>
       </c>
       <c r="C2" s="46" t="n"/>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B3" s="68" t="inlineStr">
         <is>
-          <t>01 — Youth exchange “VERIFAI: Young Detectives Against Digital Disinformation”, Beliș (Cluj County), Romania, 09/08/2027 – 15/08/2027</t>
+          <t>YEXMS01 — Youth exchange “VERIFAI: Young Detectives Against Digital Disinformation”, Beliș (Cluj County), Romania, 09/08/2027 – 15/08/2027</t>
         </is>
       </c>
       <c r="C3" s="46" t="n"/>
@@ -3034,7 +3034,7 @@
       <c r="I3" s="46" t="n"/>
       <c r="J3" s="47" t="n"/>
     </row>
-    <row r="4" ht="70" customHeight="1">
+    <row r="4" ht="122.8" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Participating organisations </t>
@@ -3042,8 +3042,8 @@
       </c>
       <c r="B4" s="48" t="inlineStr">
         <is>
-          <t>5 persons in total: 2 from GENÇ GÖNÜLLÜLER DERNEĞI (OID E10309307, Türkiye) and 2 from KEA IM Syrou (OID E10151458, Greece) — one of the two from each being a young person who will take part in the exchange — plus 1 staff member of ASOCIAȚIA GRUPUL DE ACȚIUNE LOCALĂ NAPOCA POROLISSUM (OID E10181755, Romania), the coordinating and hosting organisation.
-Requested on three grounds: all 21 participants are minors; both sending partners are new working relationships for the coordinator; and a venue's suitability cannot be assessed from photographs.</t>
+          <t>6 persons in total, two from each of the three organisations. ASOCIAȚIA GRUPUL DE ACȚIUNE LOCALĂ NAPOCA POROLISSUM (OID E10181755, Romania), organiser and host: the financial and logistics officer, who writes the venue risk assessment and signs the contract, and the Learning Programme Coordinator, registered as the facilitator on this flow. GENÇ GÖNÜLLÜLER DERNEĞI (OID E10309307, Türkiye): the proposed Turkish group leader and one young person already selected for the exchange. KEA IM Syrou (OID E10151458, Greece): the proposed Greek group leader, a social worker, and one young person already selected for the exchange.
+Requested on four grounds: all 21 participants of the exchange are minors; both sending partners are new working relationships for the coordinator; a venue's suitability cannot be assessed from photographs; and inclusion — the two young people are drawn from those who declared a situation limiting their access to opportunities, and each describes the place to their own group afterwards. Both are accompanied throughout by the adult from their own organisation, with parental consent and insurance in place.</t>
         </is>
       </c>
       <c r="C4" s="46" t="n"/>
@@ -3120,13 +3120,13 @@
       <c r="F7" s="55" t="n"/>
       <c r="G7" s="56" t="inlineStr">
         <is>
-          <t>16/06/2027</t>
+          <t>09/06/2027</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
       <c r="I7" s="56" t="inlineStr">
         <is>
-          <t>17/06/2027</t>
+          <t>11/06/2027</t>
         </is>
       </c>
       <c r="J7" s="47" t="n"/>
@@ -3170,7 +3170,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="57" t="inlineStr">
         <is>
-          <t>DAY 1 — Wednesday 16/06/2027 · The venue and the programme</t>
+          <t>DAY 1 — Wednesday 09/06/2027 · The venue and its safety</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B11" s="60" t="inlineStr">
         <is>
-          <t>On-site verification of the venue against the written risk assessment: fire safety certification and evacuation routes; the state of the electrical installations and heating; security of doors, windows and balconies; lighting of outdoor areas; separation of participant accommodation from any unrelated guests; the rooms in which minors will be accommodated only with minors, with group leaders on the same floors.</t>
+          <t>On-site verification of the accommodation unit against the written risk assessment: fire safety certification and evacuation routes; the state of the electrical installations and heating; security of doors, windows and balconies; lighting of outdoor areas; separation of participant accommodation from any unrelated guests; and the rooms in which minors will be accommodated only with minors, with group leaders on the same floors.</t>
         </is>
       </c>
       <c r="C11" s="61" t="n"/>
@@ -3207,7 +3207,7 @@
       <c r="A12" s="63" t="n"/>
       <c r="B12" s="64" t="inlineStr">
         <is>
-          <t>Measured test of the internet connection in the plenary room and in the four small-team spaces, because the whole programme depends on it; mobile signal coverage tested across the site; distance and travel time to the nearest medical facility and hospital checked in person; the reference medical facility and the first-aid arrangements identified and written down.</t>
+          <t>Measured test of the internet connection in the plenary room and in the four small-team spaces, because the whole programme depends on it, and mobile signal coverage tested across the site. The two young people check the rooms and the common spaces from a participant's point of view rather than an organiser's, and their observations are recorded.</t>
         </is>
       </c>
       <c r="C12" s="65" t="n"/>
@@ -3219,7 +3219,7 @@
       <c r="I12" s="65" t="n"/>
       <c r="J12" s="66" t="n"/>
     </row>
-    <row r="13" ht="43.6" customHeight="1">
+    <row r="13" ht="30.4" customHeight="1">
       <c r="A13" s="63" t="inlineStr">
         <is>
           <t>PM</t>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>Working session with the partners on the division of the thematic days: GGD confirms what it leads on Day 3 and Day 6 and which of its staff will be Facilitator 2; KEA confirms the Day 5 dialogue method and the local-initiative template; the coordinator confirms Days 1, 2, 4 and 7. The daily timetable is finalised session by session, in the same room and in one sitting.</t>
+          <t>The route to the nearest medical facility and hospital is driven rather than looked up, the reference facility and the first-aid arrangements are identified and written down, and the outdoor spaces to be used are inspected.</t>
         </is>
       </c>
       <c r="C13" s="65" t="n"/>
@@ -3239,11 +3239,11 @@
       <c r="I13" s="65" t="n"/>
       <c r="J13" s="66" t="n"/>
     </row>
-    <row r="14" ht="56.8" customHeight="1">
+    <row r="14" ht="30.4" customHeight="1">
       <c r="A14" s="63" t="n"/>
       <c r="B14" s="69" t="inlineStr">
         <is>
-          <t>The three measurement instruments are agreed: the fifteen-item practical test (Form A and Form B), the observation grid of four techniques scored 0–2, and the beneficiary exercise for the local initiatives; the observer calibration exercise of month 4 is scheduled. Safeguarding arrangements, the night-duty rota, the emergency protocol and the sensitive-content protocol are agreed in writing.</t>
+          <t>Negotiation with the accommodation unit on places, rooms, meals and price; the venue is either confirmed in writing with the risk assessment attached, or rejected with enough time left to find another.</t>
         </is>
       </c>
       <c r="C14" s="70" t="n"/>
@@ -3258,7 +3258,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="57" t="inlineStr">
         <is>
-          <t>DAY 2 — Thursday 17/06/2027 · The host community and the practical arrangements</t>
+          <t>DAY 2 — Thursday 10/06/2027 · The programme, the instruments and the protection arrangements</t>
         </is>
       </c>
       <c r="B15" s="46" t="n"/>
@@ -3271,7 +3271,7 @@
       <c r="I15" s="46" t="n"/>
       <c r="J15" s="58" t="n"/>
     </row>
-    <row r="16" ht="30.4" customHeight="1">
+    <row r="16" ht="43.6" customHeight="1">
       <c r="A16" s="59" t="inlineStr">
         <is>
           <t>AM</t>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B16" s="60" t="inlineStr">
         <is>
-          <t>Visit to the sites of the Day 5 community day in and around Beliș; meeting at the mayor's office and with residents who have agreed to take part in the dialogue; the route, the timing and the group transport are agreed on the spot.</t>
+          <t>Working session of the three organisations on the division of the thematic days: GGD confirms what it leads on Day 3 and Day 6 and names the staff member who will be Facilitator 2; KEA confirms the Day 5 dialogue method and the local-initiative template; the coordinator confirms Days 1, 2, 4 and 7. The daily timetable is finalised session by session, in one sitting.</t>
         </is>
       </c>
       <c r="C16" s="61" t="n"/>
@@ -3291,11 +3291,11 @@
       <c r="I16" s="61" t="n"/>
       <c r="J16" s="62" t="n"/>
     </row>
-    <row r="17" ht="30.4" customHeight="1">
+    <row r="17" ht="43.6" customHeight="1">
       <c r="A17" s="63" t="n"/>
       <c r="B17" s="64" t="inlineStr">
         <is>
-          <t>The young person from each sending organisation sees the venue, the village and the rooms, and their observations are written into the final programme — which is the reason they travel rather than a courtesy.</t>
+          <t>The three measurement instruments are agreed: the fifteen-item practical test in two equivalent forms, the observation grid of four techniques scored 0–2, and the ten-minute beneficiary exercise for the local initiatives. The observer calibration exercise of month 4 is scheduled and the pilot group for the instruments is agreed.</t>
         </is>
       </c>
       <c r="C17" s="65" t="n"/>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B18" s="64" t="inlineStr">
         <is>
-          <t>Practical arrangements settled: meals and dietary requirements with the local producers; insurance for all 27 persons; the visa file and its timetable for the Turkish group, starting five months before the activity; the ferry and flight timings for the Greek group and its four eligible travel days; the domestic transport plan from each participant's own home.</t>
+          <t>Protection arrangements are put in writing while everyone is in the same room: the safeguarding chain and who holds it in each country, the night-duty rota, the emergency protocol, the sensitive-content protocol, and the media and consent rules for content involving minors.</t>
         </is>
       </c>
       <c r="C18" s="65" t="n"/>
@@ -3327,11 +3327,11 @@
       <c r="I18" s="65" t="n"/>
       <c r="J18" s="66" t="n"/>
     </row>
-    <row r="19" ht="43.6" customHeight="1">
+    <row r="19" ht="30.4" customHeight="1">
       <c r="A19" s="63" t="n"/>
       <c r="B19" s="69" t="inlineStr">
         <is>
-          <t>Written minutes with decisions, owners and deadlines; signature of the partnership agreement annexes on safeguarding and on the division of tasks; the four joint online preparation sessions of months 3 and 4 fixed in the calendar, in mixed national composition.</t>
+          <t>The partnership agreement annexes on safeguarding and on the division of tasks are signed, and the four joint online preparation sessions of months 3 and 4 are fixed in the calendar in mixed national composition.</t>
         </is>
       </c>
       <c r="C19" s="70" t="n"/>
@@ -3343,29 +3343,118 @@
       <c r="I19" s="70" t="n"/>
       <c r="J19" s="71" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="72" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="57" t="inlineStr">
+        <is>
+          <t>DAY 3 — Friday 11/06/2027 · The host community and the practical arrangements</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
+      <c r="E20" s="46" t="n"/>
+      <c r="F20" s="46" t="n"/>
+      <c r="G20" s="46" t="n"/>
+      <c r="H20" s="46" t="n"/>
+      <c r="I20" s="46" t="n"/>
+      <c r="J20" s="58" t="n"/>
+    </row>
+    <row r="21" ht="43.6" customHeight="1">
+      <c r="A21" s="59" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>The route of the Day 5 community day is walked in and around Beliș, with the two young people taking part; meeting at the mayor's office and with residents who have agreed to take part in the dialogue; the route, the timing and the group transport are agreed on the spot.</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="61" t="n"/>
+      <c r="G21" s="61" t="n"/>
+      <c r="H21" s="61" t="n"/>
+      <c r="I21" s="61" t="n"/>
+      <c r="J21" s="62" t="n"/>
+    </row>
+    <row r="22" ht="30.4" customHeight="1">
+      <c r="A22" s="63" t="n"/>
+      <c r="B22" s="64" t="inlineStr">
+        <is>
+          <t>Meals and dietary requirements are settled with the local producers of the territory, and the spaces for the Day 7 public presentation and for the intercultural evening are identified.</t>
+        </is>
+      </c>
+      <c r="C22" s="65" t="n"/>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="65" t="n"/>
+      <c r="H22" s="65" t="n"/>
+      <c r="I22" s="65" t="n"/>
+      <c r="J22" s="66" t="n"/>
+    </row>
+    <row r="23" ht="43.6" customHeight="1">
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>Remaining logistics: insurance for all 27 persons of the exchange; the visa file and its timetable for the Turkish group, starting five months before the activity; the ferry and flight timings for the Greek group; and the domestic transport plan from each participant's own home.</t>
+        </is>
+      </c>
+      <c r="C23" s="65" t="n"/>
+      <c r="D23" s="65" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="65" t="n"/>
+      <c r="H23" s="65" t="n"/>
+      <c r="I23" s="65" t="n"/>
+      <c r="J23" s="66" t="n"/>
+    </row>
+    <row r="24" ht="30.4" customHeight="1">
+      <c r="A24" s="63" t="n"/>
+      <c r="B24" s="69" t="inlineStr">
+        <is>
+          <t>The visit closes with written minutes carrying every decision, its owner and its deadline, circulated to the three organisations within 48 hours.</t>
+        </is>
+      </c>
+      <c r="C24" s="70" t="n"/>
+      <c r="D24" s="70" t="n"/>
+      <c r="E24" s="70" t="n"/>
+      <c r="F24" s="70" t="n"/>
+      <c r="G24" s="70" t="n"/>
+      <c r="H24" s="70" t="n"/>
+      <c r="I24" s="70" t="n"/>
+      <c r="J24" s="71" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="72" t="inlineStr">
         <is>
           <t>For additional days, please copy the above rows</t>
         </is>
       </c>
-      <c r="B20" s="65" t="n"/>
-      <c r="C20" s="65" t="n"/>
-      <c r="D20" s="65" t="n"/>
-      <c r="E20" s="65" t="n"/>
-      <c r="F20" s="65" t="n"/>
-      <c r="G20" s="65" t="n"/>
-      <c r="H20" s="65" t="n"/>
-      <c r="I20" s="65" t="n"/>
-      <c r="J20" s="66" t="n"/>
+      <c r="B25" s="65" t="n"/>
+      <c r="C25" s="65" t="n"/>
+      <c r="D25" s="65" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="65" t="n"/>
+      <c r="H25" s="65" t="n"/>
+      <c r="I25" s="65" t="n"/>
+      <c r="J25" s="66" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="32">
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="B14:J14"/>
     <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="B13:J13"/>
@@ -3378,15 +3467,19 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B24:J24"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B22:J22"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="B18:J18"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B21:J21"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VERIFAI_KA152_Annex_Timetable.xlsx
+++ b/VERIFAI_KA152_Annex_Timetable.xlsx
@@ -3034,7 +3034,7 @@
       <c r="I3" s="46" t="n"/>
       <c r="J3" s="47" t="n"/>
     </row>
-    <row r="4" ht="122.8" customHeight="1">
+    <row r="4" ht="136" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Participating organisations </t>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B4" s="48" t="inlineStr">
         <is>
-          <t>6 persons in total, two from each of the three organisations. ASOCIAȚIA GRUPUL DE ACȚIUNE LOCALĂ NAPOCA POROLISSUM (OID E10181755, Romania), organiser and host: the financial and logistics officer, who writes the venue risk assessment and signs the contract, and the Learning Programme Coordinator, registered as the facilitator on this flow. GENÇ GÖNÜLLÜLER DERNEĞI (OID E10309307, Türkiye): the proposed Turkish group leader and one young person already selected for the exchange. KEA IM Syrou (OID E10151458, Greece): the proposed Greek group leader, a social worker, and one young person already selected for the exchange.
+          <t>6 persons in total, two from each of the three organisations. ASOCIAȚIA GRUPUL DE ACȚIUNE LOCALĂ NAPOCA POROLISSUM (OID E10181755, Romania), organiser and host: Alina Ioana Baba, project manager, who contracts the venue and takes the risk decision, and Livia Golovatic, activity coordinator and Romanian group leader, who runs the joint online preparation that follows. GENÇ GÖNÜLLÜLER DERNEĞI (OID E10309307, Türkiye): the facilitator it designates for the exchange — the one facilitator counted on this activity — and one young person already selected for the exchange. KEA IM Syrou (OID E10151458, Greece): Evgenia Kalogeropoulou, social worker and proposed Greek group leader, and one young person already selected for the exchange.
 Requested on four grounds: all 21 participants of the exchange are minors; both sending partners are new working relationships for the coordinator; a venue's suitability cannot be assessed from photographs; and inclusion — the two young people are drawn from those who declared a situation limiting their access to opportunities, and each describes the place to their own group afterwards. Both are accompanied throughout by the adult from their own organisation, with parental consent and insurance in place.</t>
         </is>
       </c>

--- a/VERIFAI_KA152_Annex_Timetable.xlsx
+++ b/VERIFAI_KA152_Annex_Timetable.xlsx
@@ -3034,7 +3034,7 @@
       <c r="I3" s="46" t="n"/>
       <c r="J3" s="47" t="n"/>
     </row>
-    <row r="4" ht="136" customHeight="1">
+    <row r="4" ht="149.2" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Participating organisations </t>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B4" s="48" t="inlineStr">
         <is>
-          <t>6 persons in total, two from each of the three organisations. ASOCIAȚIA GRUPUL DE ACȚIUNE LOCALĂ NAPOCA POROLISSUM (OID E10181755, Romania), organiser and host: Alina Ioana Baba, project manager, who contracts the venue and takes the risk decision, and Livia Golovatic, activity coordinator and Romanian group leader, who runs the joint online preparation that follows. GENÇ GÖNÜLLÜLER DERNEĞI (OID E10309307, Türkiye): the facilitator it designates for the exchange — the one facilitator counted on this activity — and one young person already selected for the exchange. KEA IM Syrou (OID E10151458, Greece): Evgenia Kalogeropoulou, social worker and proposed Greek group leader, and one young person already selected for the exchange.
+          <t>Six people take part and four of them are funded. Funded travellers: GENÇ GÖNÜLLÜLER DERNEĞI (OID E10309307, Türkiye) — the facilitator it designates for the exchange, who is the one facilitator counted on this activity, and one young person already selected for the exchange; KEA IM Syrou (OID E10151458, Greece) — Evgenia Kalogeropoulou, social worker and proposed Greek group leader, and one young person already selected. Taking part on site at no cost to the project: ASOCIAȚIA GRUPUL DE ACȚIUNE LOCALĂ NAPOCA POROLISSUM (OID E10181755, Romania), organiser and host — Alina Ioana Baba, project manager, who contracts the venue and takes the risk decision, and Livia Golovatic, activity coordinator and Romanian group leader, who runs the joint online preparation that follows. Both are local, so no unit cost is claimed.
 Requested on four grounds: all 21 participants of the exchange are minors; both sending partners are new working relationships for the coordinator; a venue's suitability cannot be assessed from photographs; and inclusion — the two young people are drawn from those who declared a situation limiting their access to opportunities, and each describes the place to their own group afterwards. Both are accompanied throughout by the adult from their own organisation, with parental consent and insurance in place.</t>
         </is>
       </c>
